--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:03+00:00</t>
+    <t>2023-03-24T14:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:14+00:00</t>
+    <t>2023-03-24T14:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:11+00:00</t>
+    <t>2023-03-24T14:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:59+00:00</t>
+    <t>2023-03-24T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:20+00:00</t>
+    <t>2023-03-24T15:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:53+00:00</t>
+    <t>2023-03-26T08:42:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:42:47+00:00</t>
+    <t>2023-03-26T09:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:01:05+00:00</t>
+    <t>2023-03-26T09:02:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:02:01+00:00</t>
+    <t>2023-03-26T10:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:39+00:00</t>
+    <t>2023-03-26T10:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:51+00:00</t>
+    <t>2023-03-26T11:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:08:41+00:00</t>
+    <t>2023-03-26T11:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:16:53+00:00</t>
+    <t>2023-03-26T11:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:17:47+00:00</t>
+    <t>2023-03-27T11:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:35:12+00:00</t>
+    <t>2023-03-27T12:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:01:10+00:00</t>
+    <t>2023-03-27T12:02:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:02:15+00:00</t>
+    <t>2023-03-28T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:37:59+00:00</t>
+    <t>2023-03-28T07:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:45:58+00:00</t>
+    <t>2023-03-29T10:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:46:03+00:00</t>
+    <t>2023-03-29T10:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:52:43+00:00</t>
+    <t>2023-03-31T13:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:54:07+00:00</t>
+    <t>2023-03-31T13:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:55:03+00:00</t>
+    <t>2023-04-01T08:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:28:06+00:00</t>
+    <t>2023-04-01T08:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:29:12+00:00</t>
+    <t>2023-04-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:49:37+00:00</t>
+    <t>2023-04-01T08:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:50:39+00:00</t>
+    <t>2023-04-03T09:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:35:38+00:00</t>
+    <t>2023-04-03T09:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:37:11+00:00</t>
+    <t>2023-04-03T10:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:19:29+00:00</t>
+    <t>2023-04-03T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:20:09+00:00</t>
+    <t>2023-04-04T06:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:46:45+00:00</t>
+    <t>2023-04-04T06:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:47:21+00:00</t>
+    <t>2023-04-04T08:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:23:07+00:00</t>
+    <t>2023-04-04T08:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:37:07+00:00</t>
+    <t>2023-04-04T09:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:08:50+00:00</t>
+    <t>2023-04-04T09:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:09:26+00:00</t>
+    <t>2023-04-04T09:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:19:23+00:00</t>
+    <t>2023-04-04T09:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:25:44+00:00</t>
+    <t>2023-04-04T10:05:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:22+00:00</t>
+    <t>2023-04-04T10:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:29+00:00</t>
+    <t>2023-04-04T10:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:21:49+00:00</t>
+    <t>2023-04-04T10:30:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:30:43+00:00</t>
+    <t>2023-04-04T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:10+00:00</t>
+    <t>2023-04-04T10:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:37+00:00</t>
+    <t>2023-04-04T13:12:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:16+00:00</t>
+    <t>2023-04-04T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:12+00:00</t>
+    <t>2023-04-17T11:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:49:04+00:00</t>
+    <t>2023-04-17T12:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:05:39+00:00</t>
+    <t>2023-05-26T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -272,7 +272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -361,37 +361,45 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="B16" t="s" s="2">
         <v>27</v>
       </c>
     </row>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:00:29+00:00</t>
+    <t>2023-06-13T16:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,10 +260,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>

--- a/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
+++ b/branches/Add-laboratory-definitions/ValueSet-vs-specimen-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
